--- a/Data/Lambayeque/noticias_lambayeque_20260928_20261005.xlsx
+++ b/Data/Lambayeque/noticias_lambayeque_20260928_20261005.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -470,24 +470,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Chiclayo (Lambayeque)</t>
+          <t>Usuarios de Pensión 65 inician cobro de subvención en los 24 departamentos del país</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 96.264% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:02.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>De acuerdo con información del Midis, liderado por la ministra Maritza Canales , Cajamarca (90 204), Lima (74 298) y Puno (72 529) son las zonas que tienen mayor cantidad de población coberturada.
+La lista continúa con Piura (64 402), Cusco (58 344), Áncash (47 934), La Libertad (42 007), Ayacucho (41 107), Junín (39 655), Loreto (39 401), Huánuco (37 420), San Martín (35 942), Apurímac (32 928), Huancavelica (29 034), Lambayeque (26 905), Amazonas (20 534), Ucayali (19 333), Arequipa (15 878), Pasco (9499), Ica (9066), Tumbes (7003), Tacna (4345), Moquegua (3978) y Madre de Dios (2605).
+De los 824 351 usuarios, más de 760 000 retiran el soporte económico con una tarjeta de débito.
+Al respecto, los adultos mayores reciben charlas de inclusión financiera para que conozcan cómo usar esta herramienta y la importancia de que no compartan sus claves.
+Cabe precisar que los promotores de Pensión 65, quienes orientan a la población, recorren el país debidamente identificados, con su fotocheck visible y el chaleco institucional.
+Asimismo, es importante indicar que los equipos de las unidades territoriales del programa social no piden las tarjetas de débitos.
+“A la fecha, hay 760 000 adultos mayores que utilizan esta importante herramienta que brindamos en campañas de modernización del cobro.
+Además, el personal sigue capacitando a la población para que sepa usar este instrumento y conozca la importancia de no compartir su clave secreta”, detalló la titular del Midis.
+Más en Andina ?? Mira los resultados de las elecciones en la región, provincia y distritos del Callao, según la ONPE https://t.co/IK0PiA7Mre https://t.co/zSjwXbAH3b (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 5, 2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-chiclayo-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-usuarios-pension-65-inician-cobro-subvencion-los-24-departamentos-del-pais-1094720.aspx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -495,17 +503,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Lambayeque</t>
+          <t>ONPE procesó el 100 % de actas de mesas de Lima Metropolitana y cinco regiones</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 95.06% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:02.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Del total de mesas, 24,427 actas (el 92.699 %) fueron contabilizadas; es decir, los votos registrados en ellas entraron al cómputo de los resultados electorales.
+Lea también: ERM 2026: ¿Qué falta para conocer los resultados finales de la elección? Otras 1,924 actas (el 7.301 %) no pudieron ser contabilizadas debido a que fueron objeto de una observación o contienen una solicitud de impugnación o nulidad formulada durante el escrutinio.
+Por ello, fueron remitidas al jurado electoral especial respectivo para que lo evalúe y resuelva.
+También se procesó la totalidad de actas electorales de las regiones de Callao, Tumbes, Lambayeque, Moquegua e Ica, puntualizó la ONPE.
+La entidad electoral indicó que procesa con rapidez y precisión las actas que están ingresando a sus 125 centros de cómputo, ubicados en el mismo número de oficinas descentralizadas de procesos electorales (ODPE).
+Tras culminar la jornada del domingo 4 de octubre, la ONPE habilitó la página web de resultados donde muestra el avance en el procesamiento de las actas elaboradas por los miembros de mesa.
+Cualquier persona puede ingresar y conocer la cantidad de votos emitidos en las 89,935 mesas de sufragio que funcionaron en todo el país.
+Asimismo, es posible visualizar cada una de las actas digitalizadas, colocando el número del Documento Nacional de Identidad de un ciudadano o el número de la mesa de sufragio donde fue generada.
+Más en Andina: La presidenta de la república, Keiko Fujimori, hizo hoy un llamado a las nuevas autoridades electas en las Elecciones Regionales y Municipales 2026, para trabajar "juntos de la mano y como un gran equipo" https://t.co/pEzTOYyLC0 https://t.co/ERnSzUJsDf (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 5, 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-onpe-proceso-100-actas-mesas-lima-metropolitana-y-cinco-regiones-1094709.aspx</t>
         </is>
       </c>
     </row>
@@ -525,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ferreñafe, según el conteo oficial de la ONPE al 96.417% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:02.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ferreñafe, según el conteo oficial de la ONPE al 98.371% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:22.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -550,7 +566,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 90.828% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 08:02.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 97.987% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 09:02.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,21 +582,21 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Manuel Antonio Mesones Muro (Lam...</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Chiclayo (Lambayeque)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Chiclayo, según el conteo oficial de la ONPE al 98.069% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 10:22.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-manuel-antonio-mesones-muro-lambayeque-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-chiclayo-lambayeque-noticia/</t>
         </is>
       </c>
     </row>
@@ -591,21 +607,21 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Jayanca (Lambayeque)</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Lambayeque</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Lambayeque, según el conteo oficial de la ONPE al 98.27% , arroja el siguiente resultado (actualizado el 05/10/2026, a las 13:16.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-jayanca-lambayeque-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-lambayeque-noticia/</t>
         </is>
       </c>
     </row>
@@ -616,78 +632,137 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Morrope (Lambayeque)</t>
+          <t>Resultados ONPE en región Lambayeque: revisa aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-morrope-lambayeque-noticia/</t>
+          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Motupe (Lambayeque)</t>
+          <t>Empleo en el Perú: formas de reclutamiento y de contratación requieren actualización</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Bajo esa premisa, se realizó el Encuentro Empresarial 2026: Empresas que generan empleo , organizado con el apoyo de la Unión Europea (UE) y que reunió a representantes del sector privado, instituciones públicas y organizaciones de cooperación.
+El estudio analizó la dinámica de la oferta y la demanda laboral, e identificó las principales brechas que enfrentan las empresas para acceder a talento pertinente a sus necesidades productivas, señala artículo publicado en el Suplemento Económika del Diario El Peruano .
+Los resultados muestran que el desafío no se limita a la disponibilidad de trabajadores , sino que comprende también la correspondencia entre las competencias requeridas y las disponibles, la capacidad para atraer nuevos perfiles, la adaptación al puesto y la permanencia del talento.
+“El estudio fue realizado por un equipo de investigación interdisciplinario que visitó ocho regiones para entender lo que sucede con las empresas, para conocer qué pasa con los jóvenes y para determinar dónde están las brechas que impiden una inserción laboral sostenible”, afirmó el director de Investigaciones en Ciencias Administrativas y Recursos Humanos de la Universidad San Martín de Porres, Arístides Vara Horna.
+- Ministerio de Trabajo posibilitó a casi 9,000 peruanos acceder a un empleo formal Agregó que esas brechas generan sobrecostos para que las empresas consigan profesionales o empleados altamente productivos.
+“Los altos costos de rotación son el dolor de cabeza de las empresas, y lo que se ha buscado con este estudio es brindar una visión de cómo evitar este contratiempo”, refirió.
+Configuración territorial El estudio identifica tres configuraciones territoriales principales.
+La primera corresponde al norte agroindustrial temporal, donde la demanda laboral se encuentra estrechamente vinculada a actividades productivas que pueden presentar variaciones estacionales.
+Para las empresas, esto plantea el reto de anticipar oportunamente sus necesidades de personal, contar con trabajadores que posean las competencias requeridas y generar condiciones que favorezcan la permanencia.
+La segunda configuración corresponde a los territorios técnico-productivos, donde adquieren mayor relevancia los perfiles técnicos y operativos vinculados a las actividades productivas locales.
+En estos territorios, una de las principales oportunidades radica en fortalecer la conexión entre empresas, instituciones de formación y servicios de empleo, de manera que la capacitación responda a los puestos y competencias demandados.
+La tercera corresponde a Lima urbana diversificada, caracterizada por una demanda laboral más heterogénea y por la coexistencia de perfiles técnicos, operativos, comerciales, administrativos y especializados.
+“En este contexto, además de las competencias técnicas, cobran especial importancia las competencias digitales, socioemocionales y de adaptación a entornos laborales cambiantes”, refiere el informe.
+También identifica particularidades en Arequipa, donde confluyen características urbanas y técnico-productivas, y configura necesidades específicas de talento.
+Universo y oferta laboral El estudio, aplicado a 1,353 jóvenes, analiza las condiciones que favorecen o limitan la inserción laboral sostenible de personas de 18 a 29 años clasificadas como “NINI” en ocho regiones del Perú: Arequipa, Cajamarca, Cusco, La Libertad, Lambayeque, Lima, Moquegua y Piura.
+Plantea que la problemática no responde únicamente a características individuales, sino a una “falla de conversión”: la dificultad para transformar las capacidades, experiencias y disponibilidad de los jóvenes en oportunidades laborales accesibles, verificables y sostenibles.
+“Cuando conversamos con los jóvenes y revisamos las bases de datos nacionales, encontramos que hay una gran cantidad de ellos en las ocho regiones, alrededor de 700,000, con disposición para trabajar.
+La mayoría, el 84%, tiene secundaria completa o un nivel superior; mientras que el 42% tiene estudios técnicos o universitarios incompletos, es decir, a nivel de formación básica cumplen el perfil mínimo”, manifestó el analista.
+Asimismo, dijo, el 23.6% continúa capacitándose, pero la mitad de ese grupo no se ha certificado, es decir, se está capacitando por vías alternativas que no tienen certificación, pero que sí tienen competencias.
+“Cuando evaluamos la disponibilidad y luego de analizar la data secundaria, encontramos que el 74% de los jóvenes pueden empezar a trabajar en los próximos 15 días”, aseveró.
+En Lima y Callao Pero, ¿qué pasa en Lima y Callao específicamente? Tomando en cuenta que estas regiones concentran la mayor demanda laboral del país, Vara Horna explicó que se encontró que hay más de 53,000 puestos continuos.
+“No obstante, es aquí donde se genera el mayor problema, pues hay un alto costo para contratar personal y otro alto costo por rotación.
+Hablamos de un monto realmente elevado, pero no nos referimos a empleos ultra complejos”, subrayó.
+Precisó que la gran mayoría de esta demanda ocupacional corresponde a actividades operarias que se pueden aprender en menos de un mes de entrenamiento, como es el caso de teleoperadores, agentes de seguridad y vendedores minoristas en tiendas, entre otros miles de puestos proyectados.
+Para el director de Investigaciones en Ciencias Administrativas y Recursos Humanos de la Universidad San Martín de Porres, en el Perú hay talento disponible para cubrir plazas laborales; sin embargo, hay diferencias especiales a tomar en cuenta.
+“Por ejemplo, el 43% está disponible y está buscando empleo, es decir, está activo, pero no encuentra trabajo.
+Asimismo, un 31% está disponible, pero no está buscando empleo, por lo menos, no empleo formal”, refirió Vara Horna.
+Del mismo modo, comentó que hay un 25.7% que no está disponible en los próximos 15 días porque tiene barreras estructurales que le impiden trabajar.
+“Nos referimos a barreras de cuidado, es decir, tienen a alguien a quien cuidar en casa, ya sea una mamá o un papá enfermos, un hermano enfermo, y deben atender el hogar”, sostuvo.
+Barreras Para el analista, esta es una de las barreras más grandes para que esta gran masa de jóvenes pueda acceder a un empleo.
+Para el analista, esta constituye uno de los impedimentos más grandes para que esta masa de jóvenes acceda a un empleo.
+“Las exigencias de cuidados son una de las tareas que el Estado debe atender; la necesidad de cuidar a terceros representa un obstáculo fuerte que afecta a casi el 60% de los jóvenes, quienes no pueden asumir siquiera un trabajo a tiempo parcial”, comentó.
+Sostuvo que, en el ámbito regional, las barreras de cuidados son más intensivas en La Libertad, Arequipa y Moquegua.
+“Allí vemos que alrededor del 40% de los jóvenes no puede trabajar debido a este tipo de obligaciones de cuidados impuestas principalmente a las mujeres”, aseveró.
+Al analizar las barreras por género, se determinó que las mujeres afrontan mayores dificultades para emplearse.
+“Por más que cuenten con la formación necesaria, estas restricciones estructurales les impiden acceder al empleo y mantenerlo.
+Por ello, este constituye un reto que las empresas y el Estado deben asumir y atender en un trabajo articulado”.
+Reclutamiento Las empresas también tienen la oportunidad de explorar a esta población talentosa e incorporarla a sus filas.
+Sin embargo, es posible que las formas de reclutamiento y de contratación requieran de una actualización.
+Según Vara Horna, el 63% de las empresas que fueron visitadas para elaborar el estudio todavía utilizan la experiencia laboral como filtro básico para contratar.
+“No obstante, hay un 35% que ya no confía en la experiencia laboral previa y que se están basando en el uso de pruebas prácticas para ver si estos jóvenes tienen las competencias requeridas para hacer el trabajo y para ver si es que tienen las habilidades emocionales y sociales para mantenerse en él”, refirió el analista.
+Agregó que estos jóvenes cuentan con una amplia experiencia laboral, pero básicamente en el mercado informal, en empresas en donde la rotación es muy alta.
+“Ellos han aprendido cosas que colisionan con lo que ocurre en las empresas formales .
+Por ejemplo, en las informales el pago se efectúa en días, semanas y campañas; es dinero contante y sonante, sin descuentos.
+En la empresa privada los pagos se definen en quincenas o fin de mes, con los descuentos respectivos”, detalló el analista.
+Datos - Desde la perspectiva empresarial, se observa disposición declarada para incorporar jóvenes, pero persisten la contratación mediante contactos, los filtros de experiencia, la limitada intermediación pública y la cobertura incompleta de protección laboral.
+- Actualmente, la UE junto a sus socios estratégicos como la cooperación alemana para el desarrollo, implementada por la GIZ, el Instituto Ítalo-Latinoamericano (IILA), y la Cámara de Comercio de Lima (CCL), promueven alianzas con el Estado, empresas e instituciones de formación con el fin de acercar la formación a las necesidades empresariales, promover la certificación de competencias y ampliar las oportunidades de prácticas y experiencia laboral.
+- 389,000 jóvenes NINI (no estudian, no trabajan ni participan en actividades de formación), aproximadamente, concentran Lima y Callao.
+Más en Andina: ?? Mipymes y productores de 13 regiones lograron expectativas de negocios por US$ 11.4 millones en Expoalimentaria 2026, con 757 citas comerciales ante compradores nacionales e internacionales.
+?? https://t.co/PmYDWm9jrm https://t.co/ZrDIXrsaQn (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-motupe-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-empleo-el-peru-formas-reclutamiento-y-contratacion-requieren-actualizacion-1094551.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Illimo (Lambayeque)</t>
+          <t>Resultados ONPE en Lambayeque: Somos Perú lidera votos válidos, pero no alcanza el 30 %</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>De acuerdo con la imagen del reporte de la ONPE , actualizada a las 10:06 horas del 5 de octubre, con el 98.130 % de las actas contabilizadas, el Partido Democrático Somos Perú cuyo candidato es Martín Perales Saavedra ocupa el primer lugar con 28.396 % de los votos válidos.
+En segundo lugar aparece Fuerza Popular con el candidato Rolando Barboza Díaz, con 19.666 %, mientras que Avanza País-Partido de Integración Social alcanza el 10.780 %.
+La diferencia entre las dos primeras fuerzas supera los nueve puntos porcentuales.
+La clave está en el 30 % El escenario resulta especialmente relevante porque, conforme a la Ley de Elecciones Regionales, la fórmula de gobernador y vicegobernador necesita obtener no menos del 30 % de los votos válidos para ser elegida en primera vuelta.
+Si ninguna fórmula supera ese porcentaje, corresponde una segunda elección entre las dos organizaciones políticas con mayor votación.
+Con el porcentaje mostrado por la ONPE, Somos Perú todavía se encuentra por debajo del 30 %, por lo que Lambayeque quedaría encaminado a una definición en segunda vuelta entre Somos Perú y Fuerza Popular, siempre que estos resultados sean confirmados una vez culminado el procesamiento y la resolución de las actas correspondientes.
+El JNE ha señalado que las actas observadas, votos impugnados o pedidos de nulidad son remitidos a los Jurados Electorales Especiales para su respectiva resolución, por lo que los resultados de la ONPE deben ser considerados como parte del proceso de cómputo y no como una proclamación definitiva.
+El dato convierte a Lambayeque en una de las regiones que concentra la atención del escenario electoral nacional.
+La carrera por el Gobierno Regional aún no está cerrada: el primer lugar está definido provisionalmente, pero la gobernación tendrá que esperar la culminación del proceso electoral y, de confirmarse que ninguna fórmula supera el 30 %, una segunda jornada electoral.
+El JNE ya ha establecido que, cuando ninguna fórmula alcanza el 30 % de los votos válidos, la segunda elección regional se realiza entre las dos candidaturas más votadas, conforme al marco electoral vigente.
+Más en Andina: Resultados ONPE en La Libertad ?? Al 95.48%, Somos Perú y Podemos disputan el primer lugar https://t.co/3YRpPHxAY2 https://t.co/xHfyyTz1oU (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 5, 2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-illimo-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-resultados-onpe-lambayeque-somos-peru-lidera-votos-validos-pero-no-alcanza-30--1094669.aspx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -695,24 +770,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Mochumi (Lambayeque)</t>
+          <t>Puno: garantizan continuidad en la educación de niños de Centros de Acogida Residencial</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Se considera necesario, en ese sentido, “mitigar el riesgo de deserción y exclusión pedagógica de los menores albergados en los CAR, asegurando que las contingencias socioeconómicas o de índole privada de las instituciones educativas no afecten su bienestar emocional ni su continuidad en el sistema escolar”.
+Elo quedó establecido en la ordenanza regional 000010-2026-GRP/GR PUNO , que aparece en la edición de hoy del Diario Oficial El Peruano, en su separata de normas legales.
+Sus alcances comprenden a los CAR ‘Virgen de la Candelaria’ de Salcedo y ‘Niño San Salvador’ de Capachica.
+[Lea también: Estudiantes de Amazonas desarrollan dispositivo que detecta la anemia en solo 20 segundos ] Esto implica que los menores acogidos en los CAR “no sean objeto de condicionamiento, restricción o impedimento alguno para su matrícula, permanencia, asistencia, participación o continuidad educativa por razones económicas o por la falta de pago de cuotas, aportes, contribuciones, actividades o conceptos vinculados con la prestación del servicio educativo”.
+Se trata de medidas de alcance regional “destinadas a garantizar el acceso, matrícula, permanencia, participación y continuidad educativa” de los menores que se encuentran en los CAR de Puno.
+Pago por Apafa Se indica también que las cuotas ordinarias, extraordinarias, multas, aportes u otras obligaciones relacionadas con las Asociaciones de Padres de Familia no podrán ser exigidas a los menores acogidos en los CAR, ni a las entidades o personas que ejerzan su protección , como condición o impedimento para su matrícula, permanencia y asistencia en el servicio educativo público.
+Se señala que ello responde al principio “del interés superior del niño, el derecho fundamental a la educación, la igualdad de oportunidades y el principio de gratuidad de la educación pública”.
+[Lea también: Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en Lambayeque ] La aplicación de esta ordenanza estará a cargo de la Dirección Regional de Educación de Puno, las Unidades de Gestión Educativa Local, las instituciones educativas públicas de educación básica y demás órganos y entidades del gobierno regional puneño.
+Que estas medidas sean materia de una ordenanza regional responde a que se busca “establecer una regulación de carácter general, permanente y de aplicación dentro del ámbito competencial regional”.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-mochumi-lambayeque-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-puno-garantizan-continuidad-la-educacion-ninos-centros-acogida-residencial-1094537.aspx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -720,10 +803,427 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Mochumi (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-mochumi-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Pacora (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-pacora-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Salas (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-salas-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Olmos (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-olmos-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Tucume (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-tucume-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de San Jose (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-san-jose-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Illimo (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-illimo-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Motupe (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-motupe-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Morrope (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-morrope-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Jayanca (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-jayanca-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Manuel Antonio Mesones Muro (Lam...</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-manuel-antonio-mesones-muro-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Pitipo (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-pitipo-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Cañaris (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-canaris-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>César Perales lidera las elecciones en Lambayeque según boca de urna de Datum | ERM 2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre, los ciudadanos de Lambayeque acudieron a las urnas para elegir a sus próximas autoridades regionales. De acuerdo con el primer resultado de la boca de urna de Datum de las Elecciones Regionales y Municipales 2026, César Perales se ubica en el primer lugar de las preferencias para la elección de gobernador regional, con 27.5%. En segundo lugar aparece Rolando Barboza, representante de Fuerza Popular, con 18%. En tanto, Juan Carrasco, de Avanza País, obtiene 11.6% y se ubica en el tercer lugar, según este primer reporte. El resultado corresponde a la medición de boca de urna realizada por Datum durante la jornada electoral. Se trata de un primer resultado y no reemplaza el conteo oficial de votos, por lo que los porcentajes podrían variar conforme avance el procesamiento de las actas. Para definir la elección en primera vuelta, el candidato a gobernador regional debe obtener más del 30% de los votos válidos. Si ninguna candidatura supera ese porcentaje, los dos postulantes con mayor votación deberán disputar una segunda vuelta, en la que se definirá quién asumirá el gobierno regional para el próximo periodo. Más de 26.3 millones de electores estuvieron habilitados para participar en estas elecciones. Las propuestas presentadas durante la campaña estuvieron relacionadas, entre otros asuntos, con seguridad, transporte, salud y cuidado del medio ambiente. Los porcentajes de Datum corresponden a una fotografía preliminar de la jornada electoral. La posición de los candidatos podrá modificarse cuando se conozcan los resultados oficiales y se incorporen las actas procesadas. La Oficina Nacional de Procesos Electorales (ONPE) estará a cargo del procesamiento de las actas electorales y de la publicación de los resultados oficiales. El Comercio actualizará la información correspondiente conforme avance el conteo de votos.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/lima/flash-datum-en-lambayeque-resultados-de-la-elecciones-regionales-y-municipales-2026-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boca de urna: Lambayeque es otra de las regiones donde se realizaría segunda vuelta</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Este resultado arrojó la encuesta a boca de urna realizada por la empresa Datum, al término de las Elecciones Regionales y Municipales (ERM) 2026.
+En el tercer lugar se ubica Juan Carrasco de Avanza País, con 11.6% y en el cuarto puesto Saúl Milián, de Juntos por el Perú, con el 9.5%.
+La Ley de Elecciones Regionales establece que la fórmula para gobernador y vicegobernador debe obtener no menos del 30% de los votos válidos para ser elegida en primera vuelta.
+El Jurado Nacional de Elecciones (JNE) fijó el 29 de noviembre de 2026 como fecha para una eventual Segunda Elección Regional (SER).
+Más en Andina: El virtual gobernador regional de Junín es el médico Fernando Orihuela Rojas de Podemos Perú al obtener el 32.1% de las votaciones, de acuerdo a boca de urna https://t.co/4xTxlN0isu https://t.co/ne6IWNyB2X (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 5, 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-boca-urna-lambayeque-es-otra-las-regiones-donde-se-realizaria-segunda-vuelta-1094612.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales: jornada electoral en Ica se desarrolla con normalidad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>El jefe de la ODPE Ica, Villadigno Zárate Quispe, informó que la primera mesa en instalarse fue la número 021772, a las 05:45 horas, en la Institución Educativa Daniel Merino Ruiz, ubicada en el distrito de La Tinguiña, provincia y región Ica.
+Asimismo, detalló que en este centro de votación se instalaron 42 mesas de sufragio, donde un total de 12,504 electores acudirán a cumplir con su deber cívico.
+Zárate Quispe precisó que la jurisdicción de la ODPE Ica abarca las provincias de Ica, Palpa y Nasca, zonas en las cuales se instalaron 1,372 mesas de sufragio en 145 locales de votación, con el fin de atender a los 407,320 electores habilitados.
+“Los miembros de mesa que no cumplan con esta función estarán sujetos a una multa de S/ 275.
+Asimismo, los ciudadanos que no acudan a votar deberán pagar una multa por omisión al sufragio, cuyo monto depende de la clasificación socioeconómica del distrito: S/ 110 en los distritos considerados no pobres, S/ 55 en los pobres no extremos y S/ 27.50 en los pobres extremos”, señaló la autoridad electoral.
+Palpeños acuden a votar Desde las 07:00 horas, los palpeños participan en los comicios.
+La I.E.
+Raúl Porras Barrenechea figura como el centro de votación más grande, con 3,362 electores.
+En tanto, en la I.E.
+Fermín Tanguis, la mesa 023632 fue la primera en instalarse, a las 06:32 horas.
+Por su parte en la ODPE Chincha, su jurisdicción comprende las provincias de Chincha y Pisco, donde se habilitaron 1,062 mesas de sufragio distribuidas en 116 locales de votación, para un padrón de 313,562 ciudadanos.
+Operativo de control El gerente regional de Control de Ica, David Quiroga, recorrió diversos centros de votación para constatar la labor de los auditores en el marco del Operativo de Control de las Elecciones Regionales y Municipales (ERM) 2026.
+Esta intervención tiene como eje central la “ruta del gasto electoral” y busca garantizar que los recursos públicos administrados por la ONPE y el JNE —destinados a material electoral, transporte, personal y servicios— se ejecuten en estricto cumplimiento de la legalidad y conforme a las condiciones contractuales establecidas.
+Más en Andina: ??? Las Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en los principales centros de votación de Lambayeque, mientras el Ministerio Público mantiene un despliegue preventivo de 170 fiscales para supervisar el proceso ?? https://t.co/ptVlZpsbQC https://t.co/X7o1pxn8ad (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-elecciones-regionales-y-municipales-jornada-electoral-ica-se-desarrolla-normalidad-1094514.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Sistema electoral suspende elecciones en colegio de Celendín tras registrarse incendio</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Fiscalía realiza diligencias El Ministerio Público confirmó el incidente y precisó que la Fiscalía Penal de Turno de Celendín realiza diligencias en la I.
 E.
@@ -753,306 +1253,27 @@
 ?? https://t.co/mD07ZTpEY9 https://t.co/MjUblaToyu (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-sistema-electoral-suspende-elecciones-colegio-celendin-tras-registrarse-incendio-1094546.aspx</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Tucume (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-tucume-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Olmos (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-olmos-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Salas (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-salas-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Pacora (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-pacora-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Resultados ONPE en región Lambayeque: conoce aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios iniciaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación en región Lambayeque según primeros resultados de la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-lambayeque-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>César Perales lidera las elecciones en Lambayeque según boca de urna de Datum | ERM 2026</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre, los ciudadanos de Lambayeque acudieron a las urnas para elegir a sus próximas autoridades regionales. De acuerdo con el primer resultado de la boca de urna de Datum de las Elecciones Regionales y Municipales 2026, César Perales se ubica en el primer lugar de las preferencias para la elección de gobernador regional, con 27.5%. En segundo lugar aparece Rolando Barboza, representante de Fuerza Popular, con 18%. En tanto, Juan Carrasco, de Avanza País, obtiene 11.6% y se ubica en el tercer lugar, según este primer reporte. El resultado corresponde a la medición de boca de urna realizada por Datum durante la jornada electoral. Se trata de un primer resultado y no reemplaza el conteo oficial de votos, por lo que los porcentajes podrían variar conforme avance el procesamiento de las actas. Para definir la elección en primera vuelta, el candidato a gobernador regional debe obtener más del 30% de los votos válidos. Si ninguna candidatura supera ese porcentaje, los dos postulantes con mayor votación deberán disputar una segunda vuelta, en la que se definirá quién asumirá el gobierno regional para el próximo periodo. Más de 26.3 millones de electores estuvieron habilitados para participar en estas elecciones. Las propuestas presentadas durante la campaña estuvieron relacionadas, entre otros asuntos, con seguridad, transporte, salud y cuidado del medio ambiente. Los porcentajes de Datum corresponden a una fotografía preliminar de la jornada electoral. La posición de los candidatos podrá modificarse cuando se conozcan los resultados oficiales y se incorporen las actas procesadas. La Oficina Nacional de Procesos Electorales (ONPE) estará a cargo del procesamiento de las actas electorales y de la publicación de los resultados oficiales. El Comercio actualizará la información correspondiente conforme avance el conteo de votos.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/lima/flash-datum-en-lambayeque-resultados-de-la-elecciones-regionales-y-municipales-2026-erm-2026-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Pitipo (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-pitipo-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Cañaris (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-canaris-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de San Jose (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-san-jose-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Boca de urna: Lambayeque es otra de las regiones donde se realizaría segunda vuelta</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Este resultado arrojó la encuesta a boca de urna realizada por la empresa Datum, al término de las Elecciones Regionales y Municipales (ERM) 2026.
-En el tercer lugar se ubica Juan Carrasco de Avanza País, con 11.6% y en el cuarto puesto Saúl Milián, de Juntos por el Perú, con el 9.5%.
-La Ley de Elecciones Regionales establece que la fórmula para gobernador y vicegobernador debe obtener no menos del 30% de los votos válidos para ser elegida en primera vuelta.
-El Jurado Nacional de Elecciones (JNE) fijó el 29 de noviembre de 2026 como fecha para una eventual Segunda Elección Regional (SER).
-Más en Andina: El virtual gobernador regional de Junín es el médico Fernando Orihuela Rojas de Podemos Perú al obtener el 32.1% de las votaciones, de acuerdo a boca de urna https://t.co/4xTxlN0isu https://t.co/ne6IWNyB2X (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 5, 2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-boca-urna-lambayeque-es-otra-las-regiones-donde-se-realizaria-segunda-vuelta-1094612.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Chochope (Lambayeque)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/politica/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-chochope-lambayeque-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C24" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>ERM 2026: Reniec atendió en la última semana más de 19 mil solicitudes de DNI vía web</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Con esta acción, el Reniec atendió de manera oportuna a miles de ciudadanos que requerían recuperar su documento de identidad antes de la jornada electoral, asegurando las condiciones necesarias para ejercer su derecho al voto.
 Lee también: ERM 2026: supervisan la seguridad de la jornada desde Central de Operaciones de la PNP El servicio excepcional de DNI Exprés estuvo disponible hasta hoy en las 27 agencias habilitadas a nivel nacional de Lima, Callao, Cajamarca, Lambayeque, Áncash, La Libertad, Ayacucho, Huánuco, Ica, Loreto, Ucayali, Puno, Tacna y Arequipa.
@@ -1060,137 +1281,64 @@
 https://t.co/hWmokUxlHB https://t.co/9d0bmh3k7j (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 3, 2026</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-erm-2026-reniec-atendio-la-ultima-semana-mas-19-mil-solicitudes-dni-via-web-1094544.aspx</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Puno: garantizan continuidad en la educación de niños de Centros de Acogida Residencial</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Se considera necesario, en ese sentido, “mitigar el riesgo de deserción y exclusión pedagógica de los menores albergados en los CAR, asegurando que las contingencias socioeconómicas o de índole privada de las instituciones educativas no afecten su bienestar emocional ni su continuidad en el sistema escolar”.
-Elo quedó establecido en la ordenanza regional 000010-2026-GRP/GR PUNO , que aparece en la edición de hoy del Diario Oficial El Peruano, en su separata de normas legales.
-Sus alcances comprenden a los CAR ‘Virgen de la Candelaria’ de Salcedo y ‘Niño San Salvador’ de Capachica.
-[Lea también: Estudiantes de Amazonas desarrollan dispositivo que detecta la anemia en solo 20 segundos ] Esto implica que los menores acogidos en los CAR “no sean objeto de condicionamiento, restricción o impedimento alguno para su matrícula, permanencia, asistencia, participación o continuidad educativa por razones económicas o por la falta de pago de cuotas, aportes, contribuciones, actividades o conceptos vinculados con la prestación del servicio educativo”.
-Se trata de medidas de alcance regional “destinadas a garantizar el acceso, matrícula, permanencia, participación y continuidad educativa” de los menores que se encuentran en los CAR de Puno.
-Pago por Apafa Se indica también que las cuotas ordinarias, extraordinarias, multas, aportes u otras obligaciones relacionadas con las Asociaciones de Padres de Familia no podrán ser exigidas a los menores acogidos en los CAR, ni a las entidades o personas que ejerzan su protección , como condición o impedimento para su matrícula, permanencia y asistencia en el servicio educativo público.
-Se señala que ello responde al principio “del interés superior del niño, el derecho fundamental a la educación, la igualdad de oportunidades y el principio de gratuidad de la educación pública”.
-[Lea también: Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en Lambayeque ] La aplicación de esta ordenanza estará a cargo de la Dirección Regional de Educación de Puno, las Unidades de Gestión Educativa Local, las instituciones educativas públicas de educación básica y demás órganos y entidades del gobierno regional puneño.
-Que estas medidas sean materia de una ordenanza regional responde a que se busca “establecer una regulación de carácter general, permanente y de aplicación dentro del ámbito competencial regional”.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-puno-garantizan-continuidad-la-educacion-ninos-centros-acogida-residencial-1094537.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales: jornada electoral en Ica se desarrolla con normalidad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>El jefe de la ODPE Ica, Villadigno Zárate Quispe, informó que la primera mesa en instalarse fue la número 021772, a las 05:45 horas, en la Institución Educativa Daniel Merino Ruiz, ubicada en el distrito de La Tinguiña, provincia y región Ica.
-Asimismo, detalló que en este centro de votación se instalaron 42 mesas de sufragio, donde un total de 12,504 electores acudirán a cumplir con su deber cívico.
-Zárate Quispe precisó que la jurisdicción de la ODPE Ica abarca las provincias de Ica, Palpa y Nasca, zonas en las cuales se instalaron 1,372 mesas de sufragio en 145 locales de votación, con el fin de atender a los 407,320 electores habilitados.
-“Los miembros de mesa que no cumplan con esta función estarán sujetos a una multa de S/ 275.
-Asimismo, los ciudadanos que no acudan a votar deberán pagar una multa por omisión al sufragio, cuyo monto depende de la clasificación socioeconómica del distrito: S/ 110 en los distritos considerados no pobres, S/ 55 en los pobres no extremos y S/ 27.50 en los pobres extremos”, señaló la autoridad electoral.
-Palpeños acuden a votar Desde las 07:00 horas, los palpeños participan en los comicios.
-La I.E.
-Raúl Porras Barrenechea figura como el centro de votación más grande, con 3,362 electores.
-En tanto, en la I.E.
-Fermín Tanguis, la mesa 023632 fue la primera en instalarse, a las 06:32 horas.
-Por su parte en la ODPE Chincha, su jurisdicción comprende las provincias de Chincha y Pisco, donde se habilitaron 1,062 mesas de sufragio distribuidas en 116 locales de votación, para un padrón de 313,562 ciudadanos.
-Operativo de control El gerente regional de Control de Ica, David Quiroga, recorrió diversos centros de votación para constatar la labor de los auditores en el marco del Operativo de Control de las Elecciones Regionales y Municipales (ERM) 2026.
-Esta intervención tiene como eje central la “ruta del gasto electoral” y busca garantizar que los recursos públicos administrados por la ONPE y el JNE —destinados a material electoral, transporte, personal y servicios— se ejecuten en estricto cumplimiento de la legalidad y conforme a las condiciones contractuales establecidas.
-Más en Andina: ??? Las Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en los principales centros de votación de Lambayeque, mientras el Ministerio Público mantiene un despliegue preventivo de 170 fiscales para supervisar el proceso ?? https://t.co/ptVlZpsbQC https://t.co/X7o1pxn8ad (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-elecciones-regionales-y-municipales-jornada-electoral-ica-se-desarrolla-normalidad-1094514.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en Lambayeque</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>En la Institución Educativa Nacional San José de Chiclayo, las 35 mesas de sufragio quedaron instaladas aproximadamente a las 8:30 de la mañana, según informó el coordinador del local.
-La jornada electoral transcurre sin hechos de gravedad y con una afluencia de electores que se espera incremente conforme avance el día.
-Como parte del operativo de prevención, el representante del Ministerio Público del Distrito Fiscal de Lambayeque, Jorge Arteaga Vera, recorre los locales de votación, entre ellos las instituciones educativas Sofía, Rosa Flores de Oliva y San José, verificando el normal desarrollo de los comicios y atendiendo posibles incidencias.
-En diálogo con la Agencia Andina , Arteaga, informó que el despliegue fiscal comprende 638 mesas de votación y no se limita a las tres provincias de Lambayeque , pues también abarca las provincias cajamarquinas de Jaén, Cutervo y San Ignacio, que forman parte del ámbito del Distrito Fiscal de Lambayeque.
-Entre las incidencias reportadas figura un inconveniente en Jaén,Cajamarca donde inicialmente se habría impedido el ingreso de ronderos a un local de votación.
-El Ministerio Público informó que la situación viene siendo monitoreada y que los problemas registrados hasta el momento están siendo superados.
-Asimismo, se advirtió la presencia de propaganda electoral colocada en un poste cercano a un centro de votación.
-El representante fiscal señaló que, de verificarse la infracción, corresponde retirar dicha propaganda, debido a que durante la jornada electoral está prohibido realizar proselitismo en los alrededores de los locales de votación.
-Otro aspecto bajo vigilancia es el cumplimiento de la ley seca , vigente desde las 8:00 de la mañana del sábado hasta las 8:00 de la mañana del lunes.
-Hasta el momento no se han registrado detenidos por incumplir esta prohibición.
-El Ministerio Público exhortó finalmente a los ciudadanos a participar de manera responsable en la jornada electoral y respetar las restricciones establecidas por la legislación, con el objetivo de garantizar unas elecciones ordenadas, transparentes y sin hechos que alteren el ejercicio democrático.
-Más en Andina: ?? El Niño ha ocurrido al menos 120 veces en los últimos cinco siglos.
-Las culturas prehispánicas desarrollaron estrategias para enfrentar sus efectos.
-Los Mochicas, por ejemplo, construyeron complejas redes de irrigación.
-?? https://t.co/jWjkEdpY7E https://t.co/rlVYD3ZLwD (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-elecciones-regionales-y-municipales-2026-se-desarrollan-normalidad-lambayeque-1094506.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Transfieren S/ 4.8 millones para continuidad de Plataformas Itinerantes de Acción Social</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Así lo determinó a través del Decreto Supremo Nº 211-2026-EF, publicado hoy en la separata de Normas Legales del diario oficial El Peruano.
+La norma precisa que se autoriza una Transferencia de Partidas en el Presupuesto del Sector Público para el Año Fiscal 2026, hasta por la suma de 4 millones 842,210 soles, por la fuente de financiamiento Recursos Ordinarios, a favor del Ministerio de Defensa, del Ministerio de la Mujer y Poblaciones Vulnerables (Midis), del Ministerio de Cultura, del Registro Nacional de Identificación y Estado Civil (Reniec), del Gobierno Regional de Loreto, del Gobierno Regional de Puno y del Gobierno Regional de Ucayali, con cargo a los recursos del Programa de Alimentación Escolar (PAE).
+Todo ello para financiar la continuidad de la operación y mantenimiento de las Plataformas Itinerantes de Acción Social (PIAS), en el marco de la Estrategia de Acción Social con Sostenibilidad (EASS).
+Los recursos de la Transferencia de Partidas a que hace referencia el artículo 1 del presente Decreto Supremo no pueden ser destinados, bajo responsabilidad, a fines distintos para los cuales son transferidos.
+Disposición Complementaria Final Única La norma a través de la Disposición Complementaria Final Única, modifica el artículo 3 del Decreto Supremo Nº 008-2026-EF, que establece la aplicación de los límites máximos de incorporación de mayores ingresos públicos en los pliegos del Gobierno Nacional, gobiernos regionales, gobiernos locales, así como de las empresas y organismos públicos de los gobiernos regionales y gobiernos locales, mediante la incorporación de los literales i), j), k) y l), conforme al siguiente texto: “Artículo 3.
+Aplicación específica de límites máximos Para efectos de la aplicación de los límites máximos de incorporación de mayores ingresos públicos fijados en el artículo 2 del presente Decreto Supremo, no se consideran: (…) i) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y gobiernos locales de los departamentos de Lima, Lambayeque, Cajamarca, Cusco y Ucayali para financiar los gastos operativos vinculados a las actividades relacionadas con la visita de Su Santidad el Papa León XIV al Perú, que se realicen en dichos departamentos, en el marco de lo establecido en el Decreto Supremo Nº 037-2026-RE y las Actas de la comisión conformada mediante el citado Decreto, conforme sus competencias.
+j) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y gobiernos locales, para financiar intervenciones de reducción del riesgo de desastres, preparación y respuesta ante el Fenómeno El Niño (FEN), así como el resguardo de la infraestructura pública, siempre que dichas intervenciones se ejecuten en las zonas declaradas en estado de emergencia por peligro inminente o por desastre en el contexto del FEN, conforme sus competencias.
+k) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y los gobiernos locales, así como de las empresas y organismos públicos de los gobiernos regionales y los gobiernos locales, para garantizar la operatividad en materia de salud, comprendiendo las prestaciones de salud, así como en materia de saneamiento, transporte, educación y orden público y seguridad, conforme sus competencias.
+l) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional para financiar acciones de mantenimiento; proyectos de investigación y transferencia tecnológica; fiscalización ambiental; promoción y masificación del deporte a nivel nacional, así como para garantizar la continuidad de sus operaciones esenciales.” La norma lleva la rúbrica de la presidenta de la República, Keiko Fujimori; la ministra de Desarrollo e Inclusión Social, Maritza Canales Martínez; y del ministro de Economía y Finanzas, Elmer Cuba Bustinza.
+Más en Andina: ?? Arequipa destaca como una región con oportunidades para la inversión y como la segunda economía más importante del interior del país.
+Sus exportaciones pasaron de US$612 millones en 2005 a US$8,466 millones en 2025, impulsadas principalmente por la minería.
+La región representa el 5.9 % del PBI nacional.
+?? https://t.co/7CWSk6Pvmr?? Miguel de la Vega Polanco (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 14, 2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-transfieren-s-48-millones-para-continuidad-plataformas-itinerantes-accion-social-1094485.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Exportaciones peruanas generan más de 1.5 millones de empleos directos</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>En su reporte Empleo asociado a las exportaciones – julio 2026, detalló que los relacionados al rubro no tradicional fueron 786,308 y al tradicional 727,355.
 El primero retrocedió en 6%, mientras que el segundo aumentó en 27.6%.
@@ -1211,108 +1359,9 @@
 ?? https://t.co/7CWSk6Pvmr?? Miguel de la Vega Polanco (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 14, 2026</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-exportaciones-peruanas-generan-mas-15-millones-empleos-directos-1094493.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>46299</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Transfieren S/ 4.8 millones para continuidad de Plataformas Itinerantes de Acción Social</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Así lo determinó a través del Decreto Supremo Nº 211-2026-EF, publicado hoy en la separata de Normas Legales del diario oficial El Peruano.
-La norma precisa que se autoriza una Transferencia de Partidas en el Presupuesto del Sector Público para el Año Fiscal 2026, hasta por la suma de 4 millones 842,210 soles, por la fuente de financiamiento Recursos Ordinarios, a favor del Ministerio de Defensa, del Ministerio de la Mujer y Poblaciones Vulnerables (Midis), del Ministerio de Cultura, del Registro Nacional de Identificación y Estado Civil (Reniec), del Gobierno Regional de Loreto, del Gobierno Regional de Puno y del Gobierno Regional de Ucayali, con cargo a los recursos del Programa de Alimentación Escolar (PAE).
-Todo ello para financiar la continuidad de la operación y mantenimiento de las Plataformas Itinerantes de Acción Social (PIAS), en el marco de la Estrategia de Acción Social con Sostenibilidad (EASS).
-Los recursos de la Transferencia de Partidas a que hace referencia el artículo 1 del presente Decreto Supremo no pueden ser destinados, bajo responsabilidad, a fines distintos para los cuales son transferidos.
-Disposición Complementaria Final Única La norma a través de la Disposición Complementaria Final Única, modifica el artículo 3 del Decreto Supremo Nº 008-2026-EF, que establece la aplicación de los límites máximos de incorporación de mayores ingresos públicos en los pliegos del Gobierno Nacional, gobiernos regionales, gobiernos locales, así como de las empresas y organismos públicos de los gobiernos regionales y gobiernos locales, mediante la incorporación de los literales i), j), k) y l), conforme al siguiente texto: “Artículo 3.
-Aplicación específica de límites máximos Para efectos de la aplicación de los límites máximos de incorporación de mayores ingresos públicos fijados en el artículo 2 del presente Decreto Supremo, no se consideran: (…) i) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y gobiernos locales de los departamentos de Lima, Lambayeque, Cajamarca, Cusco y Ucayali para financiar los gastos operativos vinculados a las actividades relacionadas con la visita de Su Santidad el Papa León XIV al Perú, que se realicen en dichos departamentos, en el marco de lo establecido en el Decreto Supremo Nº 037-2026-RE y las Actas de la comisión conformada mediante el citado Decreto, conforme sus competencias.
-j) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y gobiernos locales, para financiar intervenciones de reducción del riesgo de desastres, preparación y respuesta ante el Fenómeno El Niño (FEN), así como el resguardo de la infraestructura pública, siempre que dichas intervenciones se ejecuten en las zonas declaradas en estado de emergencia por peligro inminente o por desastre en el contexto del FEN, conforme sus competencias.
-k) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional, los gobiernos regionales y los gobiernos locales, así como de las empresas y organismos públicos de los gobiernos regionales y los gobiernos locales, para garantizar la operatividad en materia de salud, comprendiendo las prestaciones de salud, así como en materia de saneamiento, transporte, educación y orden público y seguridad, conforme sus competencias.
-l) La incorporación de mayores ingresos públicos, incluyendo los saldos de balance, de los pliegos del Gobierno Nacional para financiar acciones de mantenimiento; proyectos de investigación y transferencia tecnológica; fiscalización ambiental; promoción y masificación del deporte a nivel nacional, así como para garantizar la continuidad de sus operaciones esenciales.” La norma lleva la rúbrica de la presidenta de la República, Keiko Fujimori; la ministra de Desarrollo e Inclusión Social, Maritza Canales Martínez; y del ministro de Economía y Finanzas, Elmer Cuba Bustinza.
-Más en Andina: ?? Arequipa destaca como una región con oportunidades para la inversión y como la segunda economía más importante del interior del país.
-Sus exportaciones pasaron de US$612 millones en 2005 a US$8,466 millones en 2025, impulsadas principalmente por la minería.
-La región representa el 5.9 % del PBI nacional.
-?? https://t.co/7CWSk6Pvmr?? Miguel de la Vega Polanco (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) September 14, 2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-transfieren-s-48-millones-para-continuidad-plataformas-itinerantes-accion-social-1094485.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>El Niño: Otass envía equipos técnicos al norte del país para reforzar preparación</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>La decisión se adoptó luego de la primera evaluación realizada en territorio por el presidente ejecutivo del OTASS, Carlos Yañez Lazo, quien recorrió estas regiones para conocer las condiciones de los sistemas, identificar puntos críticos y establecer prioridades de atención.
-A partir de esta evaluación, se dispuso el acompañamiento especializado a la Unidad Ejecutora 002 Tumbes, EPS Grau, Epsel y Sedachimbote.
-“ La preparación frente al FEN exige conocer las condiciones reales de cada prestadora y actuar con anticipación.
-Por ello, hemos dispuesto el despliegue de nuestros equipos técnicos para profundizar la evaluación, priorizar las intervenciones necesarias y acompañar la elaboración de planes de acción que permitan responder oportunamente ante posibles emergencias y contribuir a la continuidad de los servicios ”, señaló el titular del organismo, entidad adscrita al Ministerio de Vivienda, Construcción y Saneamiento (MVCS).
-Durante su permanencia en las regiones, los especialistas del OTASS trabajan junto con los equipos de las prestadoras en la priorización de la intervención de los puntos críticos, el sinceramiento de necesidades y la elaboración de fichas técnicas y cronogramas.
-Asimismo, se evalúa la disponibilidad de fondos de inversión y reservas, según corresponda, para encauzar recursos hacia las acciones prioritarias, de acuerdo con las normas vigentes y el marco regulatorio aplicable, así como las necesidades que requieran gestionar recursos adicionales ante situaciones de emergencia.
-Esta intervención forma parte de una ruta de trabajo que comprende: alinear, sincerar, planificar y ejecutar, con seguimiento permanente de las acciones priorizadas.
-De esta manera, el Otass fortalece su acompañamiento técnico a las prestadoras y contribuye a una gestión preventiva del riesgo, orientada a mejorar su capacidad de respuesta y proteger la continuidad de los servicios de agua potable y saneamiento durante el FEN 2026-2027.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-el-nino-otass-envia-equipos-tecnicos-al-norte-del-pais-para-reforzar-preparacion-1094430.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>46298</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PCM fortalece capacidades de servidores públicos en integridad y lucha contra corrupción</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>La iniciativa busca fortalecer sus conocimientos y promover la reflexión sobre los riesgos y desafíos actuales en materia de integridad pública y prevención de la corrupción.
-Lee también: [ ERM 2026: Contraloría verificó entrega adecuada de material electoral en Lima y Callao ] Las conferencias se implementan en alianza con la Escuela Nacional de Administración Pública (ENAP ), de la Autoridad Nacional del Servicio Civil (Servir) y abordan nuevos enfoques, y desafíos vinculados con la agenda de integridad pública.
-La primera sesión de este módulo, denominada “La corrupción desde el enfoque de derechos humanos e igualdad de oportunidades entre hombres y mujeres” , estuvo a cargo de Alexandra Cabrera Sánchez, directora general de la Dirección General de Derechos Humanos del Ministerio de Justicia y Derechos Humanos.
-Bajo la denominación “Corrupción e integridad pública: riesgos y desafíos contemporáneos, enfoques y nuevas fronteras”, el ciclo se desarrolla de manera virtual todos los miércoles hasta el 25 de noviembre .
-La participación es gratuita y los asistentes podrán obtener una constancia, de acuerdo con las condiciones de asistencia establecidas para cada sesión.
-Las inscripciones para las siguientes sesiones se pueden realizar a través del canal de ciclo de conferencias sobre Integridad Pública y Lucha contra la Corrupción 2026, en www.gob.pe/agendaintegridad.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-pcm-fortalece-capacidades-servidores-publicos-integridad-y-lucha-contra-corrupcion-1094451.aspx</t>
         </is>
       </c>
     </row>
@@ -1323,45 +1372,78 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lambayeque:MIMP coordina con operadores de justicia para proteger a menores ante violencia</t>
+          <t>Elecciones Regionales y Municipales 2026 se desarrollan con normalidad en Lambayeque</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Durante el encuentro, reafirmó el compromiso del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP) de fortalecer el trabajo conjunto entre las instituciones para garantizar una protección oportuna y acompañamiento seguro y así evitar que las víctimas queden desatendidas.
-En lo que va del año, los Centros Emergencia Mujer y Familia atendieron 983 casos de violencia contra niños y adolescentes en Lambayeque: 465 corresponden por violencia sexual, 274 a violencia física y 244 a violencia psicológica.
-En este espacio de coordinación participaron el presidente de la Corte Superior de Justicia, César Bravo; la administradora del módulo judicial integrado en violencia contra la mujer e integrantes del grupo familiar, Blanca Cavero Laca; y el jefe de Oficina de la Defensoría del Pueblo, Carlos Rodas.
-También la representante del jefe de la Región Policial, Alférez Sandra Sánchez Loayza, el director de la Oficina Distrital de Defensa Pública y Acceso a la Justicia, Jorge Puicón; el Fiscal Superior de Familia, Mariana Vásquez Zagaceta; la coordinadora de las fiscalías de familia, Silvia Rojas Placencia; la gerenta de programas sociales del GORE Lambayeque, Mónica Toscanelli Rodríguez, entre otros operadores de justicia.
-Mujer emprendedora Durante su visita a la región, la viceministra de la Mujer también clausuró la segunda edición del Centro de Acompañamiento para la Autonomía Económica de las Mujeres (CAAEM) del MIMP, donde 32 emprendedoras de diversos distritos de Chiclayo recibieron capacitaciones presenciales, talleres y asesorías especializadas en liderazgo, atención al cliente, posicionamiento de negocios, mentoría, comunicación y marketing.
-La representante del MIMP resaltó que la autonomía económica constituye una herramienta fundamental para ampliar las oportunidades de las mujeres y contribuir a la prevención de la violencia.
-En esa línea, señaló que el sector desarrolla una intervención integral basada en tres ejes estratégicos: autonomía económica, protección a tiempo y cuidar con dignidad.</t>
+          <t>En la Institución Educativa Nacional San José de Chiclayo, las 35 mesas de sufragio quedaron instaladas aproximadamente a las 8:30 de la mañana, según informó el coordinador del local.
+La jornada electoral transcurre sin hechos de gravedad y con una afluencia de electores que se espera incremente conforme avance el día.
+Como parte del operativo de prevención, el representante del Ministerio Público del Distrito Fiscal de Lambayeque, Jorge Arteaga Vera, recorre los locales de votación, entre ellos las instituciones educativas Sofía, Rosa Flores de Oliva y San José, verificando el normal desarrollo de los comicios y atendiendo posibles incidencias.
+En diálogo con la Agencia Andina , Arteaga, informó que el despliegue fiscal comprende 638 mesas de votación y no se limita a las tres provincias de Lambayeque , pues también abarca las provincias cajamarquinas de Jaén, Cutervo y San Ignacio, que forman parte del ámbito del Distrito Fiscal de Lambayeque.
+Entre las incidencias reportadas figura un inconveniente en Jaén,Cajamarca donde inicialmente se habría impedido el ingreso de ronderos a un local de votación.
+El Ministerio Público informó que la situación viene siendo monitoreada y que los problemas registrados hasta el momento están siendo superados.
+Asimismo, se advirtió la presencia de propaganda electoral colocada en un poste cercano a un centro de votación.
+El representante fiscal señaló que, de verificarse la infracción, corresponde retirar dicha propaganda, debido a que durante la jornada electoral está prohibido realizar proselitismo en los alrededores de los locales de votación.
+Otro aspecto bajo vigilancia es el cumplimiento de la ley seca , vigente desde las 8:00 de la mañana del sábado hasta las 8:00 de la mañana del lunes.
+Hasta el momento no se han registrado detenidos por incumplir esta prohibición.
+El Ministerio Público exhortó finalmente a los ciudadanos a participar de manera responsable en la jornada electoral y respetar las restricciones establecidas por la legislación, con el objetivo de garantizar unas elecciones ordenadas, transparentes y sin hechos que alteren el ejercicio democrático.
+Más en Andina: ?? El Niño ha ocurrido al menos 120 veces en los últimos cinco siglos.
+Las culturas prehispánicas desarrollaron estrategias para enfrentar sus efectos.
+Los Mochicas, por ejemplo, construyeron complejas redes de irrigación.
+?? https://t.co/jWjkEdpY7E https://t.co/rlVYD3ZLwD (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 4, 2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-lambayequemimp-coordina-operadores-justicia-para-proteger-a-menores-ante-violencia-1094424.aspx</t>
+          <t>https://andina.pe/agencia/noticia-elecciones-regionales-y-municipales-2026-se-desarrollan-normalidad-lambayeque-1094506.aspx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: Aquí podrás conocer los resultados oficiales de ONPE en el distrito de Chochope (Lambayeque)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizarán las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definirán, con su voto, el futuro de sus distritos, provincias y regiones. En estas ERM 2026, los ciudadanos habilitados para sufragar elegirán a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los comicios comenzarán a las 7 a.m. y durarán hasta las 5 p.m., hora en que se cerrarán los centros de votación. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) deberán asistir a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los ciudadanos que cumplan con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/politica/elecciones/elecciones-regionales-y-municipales-2026-aqui-podras-conocer-los-resultados-oficiales-de-onpe-en-el-distrito-de-chochope-lambayeque-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
         <v>46298</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Solo el 5% de las empresas peruanas cuenta con protección financiera frente a El Niño</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Sin embargo, esas medidas rara vez incluyen protección financiera: solo el 5% de las empresas peruanas cuenta actualmente con algún seguro contra desastres naturales, según estimaciones de Avla Perú.
 MEF establece disposiciones complementarias para subsidio a mototaxistas de tres regiones La exposición no se limita a los daños directos sobre infraestructura, una interrupción de carreteras, el cierre temporal de una planta o la pérdida de inventarios puede generar efectos en cadena sobre proveedores, clientes, distribución y flujo de caja.
@@ -1380,46 +1462,9 @@
 Más en Andina: ?? El 85% de los peruanos consume contenido en formato de audio https://t.co/WJuDQnnHLX pic.twitter.com/qiqVI0CNn0 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 3, 2026</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-solo-5-las-empresas-peruanas-cuenta-proteccion-financiera-frente-a-nino-1094402.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Lambayeque refuerza inspecciones de seguridad en escenarios que recibirán al papa León XIV</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>La medida comprende los espacios donde se desarrollarán las actividades programadas en Pimentel, Zaña, Chiclayo y otros puntos de la ruta papal , cuyos gobiernos locales deberán contar con sus respectivos planes de contingencia y las autorizaciones correspondientes.
-La responsable de la Dirección Desconcentrada del Instituto Nacional de Defensa Civil (Indeci)-Lambayeque, Jennifer Harvey , informó en diálogo con la Agencia Andina que las inspecciones técnicas de seguridad en edificaciones estarán a cargo de los inspectores de las municipalidades competentes.
-“Cuando un distrito no cuente con inspectores, podrá solicitar el apoyo de la Municipalidad Provincial de Chiclayo para realizar la evaluación”, anotó.
-Mencionó que en el caso de Pimentel, por la magnitud de la concentración prevista, la inspección corresponderá a la Municipalidad Provincial de Chiclayo.
-La evaluación se efectuará cuando los escenarios estén completamente acondicionados, incluyendo la instalación de sillas, distribución de espacios y determinación del aforo.
-“Todo lugar donde se alberguen personas necesita un permiso y un certificado de Defensa Civil”, explicó, al destacar que el objetivo es reducir riesgos en actividades que congregarán a una gran cantidad de asistentes.
-En paralelo se elaboran protocolos de ingreso, desplazamiento y ubicación de los asistentes, tomando como referencia los planos y las características de cada terreno.
-Las autoridades señalaron que estos protocolos se definirán conforme avancen los trabajos de acondicionamiento.
-Refirió que cada municipalidad tendrá su propio plan de contingencia, articulado con el Gobierno Regional de Lambayeque, para establecer responsabilidades y procedimientos frente a cualquier eventualidad durante las actividades de la visita papal.
-La autoridad del Indeci Lambayeque indicó que los plazos para culminar estos instrumentos dependerán del avance de los trabajos y de la disponibilidad de los planos definitivos de cada escenario.
-“Las inspecciones se intensificarán una vez que los espacios estén completamente habilitados”, concluyó.
-Más en Andina: ??? La ODPE Huancayo inició el despliegue del material electoral hacia 16 distritos y 7 centros poblados de la provincia, como parte de la preparación para las Elecciones Regionales y Municipales 2026.
-?? https://t.co/KZfEQnvNle pic.twitter.com/zCe2RHGpso (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-lambayeque-refuerza-inspecciones-seguridad-escenarios-recibiran-al-papa-leon-xiv-1094317.aspx</t>
         </is>
       </c>
     </row>
@@ -1430,31 +1475,27 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>El Niño: Ejército del Perú acelera trabajos de descolmatación en río Piura</t>
+          <t>Lambayeque:MIMP coordina con operadores de justicia para proteger a menores ante violencia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Desde el puente Independencia, en el asentamiento humano Juan de Mori del distrito de Catacaos, el titular del sector señaló que las labores de descolmatación y encauzamiento del afluente, así como el reforzamiento de diques, se encuentran dentro del cronograma previsto e incluso adelantado.
-"Estamos viniendo semanalmente, o cada diez días, para ver el progreso y nos complace constatar que estamos o dentro del cronograma de avance o, incluso, lo hemos superado.
-Y, eso nos deja tranquilos, porque vamos a llegar a tiempo ante el embate del fenómeno El Niño” , subrayó.
-Registro fotográfico Belaunde Llosa refirió que cada semana el satélite PerúSAT-1, operado por la Agencia Espacial del Perú (Conida), entrega a su despacho un registro fotográfico de los avances de las labores del Ejército en la zona y el avance está dentro del cronograma establecido.
-"Hace quince días, aquí había un bosque.
-Es evidente el avance.
-Vamos a llegar a recibir los embates del fenómeno El Niño de la manera más preparada posible" , enfatizó tras remarcar que el Gobierno priorizó la intervención de puntos críticos ante la cercanía del evento climático y el abandono de los gobiernos anteriores a desarrollar trabajos de prevención.
-22 puntos críticos "Todos los puntos críticos que representen peligro, primero, a la vida y, después, a la propiedad pública-privada se atenderán.
-Es materialmente imposible cubrir los dos mil puntos críticos recibidos de la ANA (Autoridad Nacional del Agua), porque en sesenta días no se puede atender lo que se ha dejado de hacer en nueve años" , sostuvo.
-Según lo dispuesto por el Poder Ejecutivo, al sector Defensa le corresponde intervenir 22 puntos críticos ubicados a lo largo del litoral peruano: en Tumbes, 3 puntos; en Piura, 7; en Lambayeque, 2; en La Libertad, 1; en Lima, 7; y en Ica, 2.
-Más en Andina: Programa Llamkasun Perú proyecta generar más de 59,000 empleos temporales hasta diciembre https://t.co/ZtQLMBwXBs pic.twitter.com/jaeLjluJR7 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 3, 2026</t>
+          <t>Durante el encuentro, reafirmó el compromiso del Ministerio de la Mujer y Poblaciones Vulnerables (MIMP) de fortalecer el trabajo conjunto entre las instituciones para garantizar una protección oportuna y acompañamiento seguro y así evitar que las víctimas queden desatendidas.
+En lo que va del año, los Centros Emergencia Mujer y Familia atendieron 983 casos de violencia contra niños y adolescentes en Lambayeque: 465 corresponden por violencia sexual, 274 a violencia física y 244 a violencia psicológica.
+En este espacio de coordinación participaron el presidente de la Corte Superior de Justicia, César Bravo; la administradora del módulo judicial integrado en violencia contra la mujer e integrantes del grupo familiar, Blanca Cavero Laca; y el jefe de Oficina de la Defensoría del Pueblo, Carlos Rodas.
+También la representante del jefe de la Región Policial, Alférez Sandra Sánchez Loayza, el director de la Oficina Distrital de Defensa Pública y Acceso a la Justicia, Jorge Puicón; el Fiscal Superior de Familia, Mariana Vásquez Zagaceta; la coordinadora de las fiscalías de familia, Silvia Rojas Placencia; la gerenta de programas sociales del GORE Lambayeque, Mónica Toscanelli Rodríguez, entre otros operadores de justicia.
+Mujer emprendedora Durante su visita a la región, la viceministra de la Mujer también clausuró la segunda edición del Centro de Acompañamiento para la Autonomía Económica de las Mujeres (CAAEM) del MIMP, donde 32 emprendedoras de diversos distritos de Chiclayo recibieron capacitaciones presenciales, talleres y asesorías especializadas en liderazgo, atención al cliente, posicionamiento de negocios, mentoría, comunicación y marketing.
+La representante del MIMP resaltó que la autonomía económica constituye una herramienta fundamental para ampliar las oportunidades de las mujeres y contribuir a la prevención de la violencia.
+En esa línea, señaló que el sector desarrolla una intervención integral basada en tres ejes estratégicos: autonomía económica, protección a tiempo y cuidar con dignidad.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-el-nino-ejercito-del-peru-acelera-trabajos-descolmatacion-rio-piura-1094393.aspx</t>
+          <t>https://andina.pe/agencia/noticia-lambayequemimp-coordina-operadores-justicia-para-proteger-a-menores-ante-violencia-1094424.aspx</t>
         </is>
       </c>
     </row>
@@ -1465,14 +1506,148 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>El Niño: Otass envía equipos técnicos al norte del país para reforzar preparación</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La decisión se adoptó luego de la primera evaluación realizada en territorio por el presidente ejecutivo del OTASS, Carlos Yañez Lazo, quien recorrió estas regiones para conocer las condiciones de los sistemas, identificar puntos críticos y establecer prioridades de atención.
+A partir de esta evaluación, se dispuso el acompañamiento especializado a la Unidad Ejecutora 002 Tumbes, EPS Grau, Epsel y Sedachimbote.
+“ La preparación frente al FEN exige conocer las condiciones reales de cada prestadora y actuar con anticipación.
+Por ello, hemos dispuesto el despliegue de nuestros equipos técnicos para profundizar la evaluación, priorizar las intervenciones necesarias y acompañar la elaboración de planes de acción que permitan responder oportunamente ante posibles emergencias y contribuir a la continuidad de los servicios ”, señaló el titular del organismo, entidad adscrita al Ministerio de Vivienda, Construcción y Saneamiento (MVCS).
+Durante su permanencia en las regiones, los especialistas del OTASS trabajan junto con los equipos de las prestadoras en la priorización de la intervención de los puntos críticos, el sinceramiento de necesidades y la elaboración de fichas técnicas y cronogramas.
+Asimismo, se evalúa la disponibilidad de fondos de inversión y reservas, según corresponda, para encauzar recursos hacia las acciones prioritarias, de acuerdo con las normas vigentes y el marco regulatorio aplicable, así como las necesidades que requieran gestionar recursos adicionales ante situaciones de emergencia.
+Esta intervención forma parte de una ruta de trabajo que comprende: alinear, sincerar, planificar y ejecutar, con seguimiento permanente de las acciones priorizadas.
+De esta manera, el Otass fortalece su acompañamiento técnico a las prestadoras y contribuye a una gestión preventiva del riesgo, orientada a mejorar su capacidad de respuesta y proteger la continuidad de los servicios de agua potable y saneamiento durante el FEN 2026-2027.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-el-nino-otass-envia-equipos-tecnicos-al-norte-del-pais-para-reforzar-preparacion-1094430.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PCM fortalece capacidades de servidores públicos en integridad y lucha contra corrupción</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>La iniciativa busca fortalecer sus conocimientos y promover la reflexión sobre los riesgos y desafíos actuales en materia de integridad pública y prevención de la corrupción.
+Lee también: [ ERM 2026: Contraloría verificó entrega adecuada de material electoral en Lima y Callao ] Las conferencias se implementan en alianza con la Escuela Nacional de Administración Pública (ENAP ), de la Autoridad Nacional del Servicio Civil (Servir) y abordan nuevos enfoques, y desafíos vinculados con la agenda de integridad pública.
+La primera sesión de este módulo, denominada “La corrupción desde el enfoque de derechos humanos e igualdad de oportunidades entre hombres y mujeres” , estuvo a cargo de Alexandra Cabrera Sánchez, directora general de la Dirección General de Derechos Humanos del Ministerio de Justicia y Derechos Humanos.
+Bajo la denominación “Corrupción e integridad pública: riesgos y desafíos contemporáneos, enfoques y nuevas fronteras”, el ciclo se desarrolla de manera virtual todos los miércoles hasta el 25 de noviembre .
+La participación es gratuita y los asistentes podrán obtener una constancia, de acuerdo con las condiciones de asistencia establecidas para cada sesión.
+Las inscripciones para las siguientes sesiones se pueden realizar a través del canal de ciclo de conferencias sobre Integridad Pública y Lucha contra la Corrupción 2026, en www.gob.pe/agendaintegridad.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-pcm-fortalece-capacidades-servidores-publicos-integridad-y-lucha-contra-corrupcion-1094451.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Otass capacitó a profesionales de siete EPS para identificar brechas y mejorar servicios</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>La jornada estuvo orientada a identificar brechas y definir acciones para mejorar la prestación de los servicios de agua potable y saneamiento en beneficio de la población.
+Profesionales de EPS Marañón, Epsel, Sedalib, EPS Chavín, UE 002 Tumbes, Seda Chimbote y EPS Grau, analizaron información de sus propias empresas relacionada con aspectos financieros, continuidad y presión del servicio, pérdidas de agua e información comercial.
+“A partir de este análisis, cada prestadora elaboró un diagnóstico y una hoja de ruta con acciones para los próximos 90 y 180 días”, explicó el Otass en una nota de prensa.
+“Buscamos que las EPS puedan identificar sus brechas, tomar decisiones oportunas y prevenir problemas que puedan afectar los servicios.
+Ese conocimiento debe traducirse en empresas mejor preparadas para atender a más familias”, señaló el presidente ejecutivo del Otass.
+La asistencia técnica i ncluyó la revisión de programas de inversiones y fondos de reserva frente al Fenómeno El Niño (FEN), así como el uso de herramientas financieras como el costo promedio ponderado de capital (WACC), que permite determinar el valor presente de los flujos de caja futuros y evaluar proyectos de inversión.
+Estos conocimientos contribuyen a fortalecer la gestión financiera y a promover decisiones tarifarias técnicamente sustentadas que permitan financiar mejoras y sostener los servicios, considerando la capacidad de pago de la población.
+[Lea también: Lambayeque refuerza inspecciones de seguridad en escenarios que recibirán al papa León XIV ] Estrategia con resultados La estrategia ya fue aplicada en las macrorregiones Sur y Oriente, con la participación de más de 90 profesionales de 18 EPS.
+Las evaluaciones evidenciaron que el 100 % de los participantes mejoró sus conocimientos, elevando el promedio de sus calificaciones de 9.94 a 17.06 puntos sobre 20.
+Asimismo, profesionales de siete EPS alcanzaron la calificación máxima de 20 puntos.
+“De esta manera, el Otass combina capacitación, asistencia técnica y seguimiento de acuerdo con la situación de cada prestadora: en las EPS bajo el Régimen de Apoyo Transitorio (RAT), para contribuir a superar las condiciones que determinaron su ingreso al régimen y avanzar hacia una gestión sostenible; y en las demás prestadoras, para identificar brechas de manera anticipada y prevenir su deterioro, contribuyendo a servicios de agua potable y saneamiento más confiables para la población”, refirió la institución.
+[Lea también: Inician ejecución de cuatro proyectos eléctricos en beneficio de 1.6 millones de peruanos ] Más en Andina: ?? Más de 13,000 lotes serán atendidos en octubre durante la “Maratón de la Titulación”, que llegará a 24 regiones.
+Cofopri realizará empadronamientos y atenderá casos pendientes para avanzar hacia la titulación.
+?? https://t.co/nGPPA4aFWe pic.twitter.com/fgn0V1jlXr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-otass-capacito-a-profesionales-siete-eps-para-identificar-brechas-y-mejorar-servicios-1094360.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INIA lanza concurso de becas para profesionales y técnicos agropecuarios en siete regiones</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>El objetivo de estas becas es fortalecer la capacidad técnica de profesionales y técnicos agropecuarios “para brindar servicios de calidad a las familias agricultoras del país”, detalló el INIA, en una nota de prensa.
+La convocatoria está dirigida a extensionistas agrarios, profesionales y técnicos agropecuarios “que cuenten con experiencia en la prestación de servicios de extensión agropecuaria dirigidos a productores de la agricultura familiar”, precisó la institución.
+En total, se otorgarán 510 becas para participar en los 12 cursos de formación y acreditación de PSEA, distribuidos en los departamentos de Lambayeque, Cajamarca, San Martín, Junín, Puno, Cusco y la provincia de Tayacaja (Huancavelica).
+[Lea también: Investigador del IIAP estudia cómo las aves contribuyen a la regeneración de los bosques ] Mejora de la productividad La propuesta de formación fortalecerá las capacidades de dichos profesionales para brindar servicios de extensión agropecuaria, con enfoque de género e intercultural, intergeneracional y de resiliencia al cambio climático.
+Para ello, se actualizarán sus conocimientos en aprendizaje adulto, enfoques y metodologías de extensión agropecuaria, financiamiento y comercialización, así como en innovaciones agrarias frugales pertinentes para la agricultura familiar, en los cultivos y crianzas priorizados.
+El proyecto PRED-INIA busca contribuir en la mejora de la productividad en el sector agrario del Perú, considerando la sostenibilidad ambiental y la resiliencia climática, propiciando un mayor acceso de las familias agricultoras a los servicios de innovación, transferencia tecnológica y extensión agropecuaria.
+Las bases del concurso se encuentran publicadas en la página web del INIA y las personas interesadas las pueden revisarlas visitando este enlace: clic aquí.
+[Lea también: Productores agrarios cuentan con Seguro Agrícola Catastrófico: cubre S/1,000 por hectárea ] Más en Andina: ?? Más de 13,000 lotes serán atendidos en octubre durante la “Maratón de la Titulación”, que llegará a 24 regiones.
+Cofopri realizará empadronamientos y atenderá casos pendientes para avanzar hacia la titulación.
+?? https://t.co/nGPPA4aFWe pic.twitter.com/fgn0V1jlXr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-inia-lanza-concurso-becas-para-profesionales-y-tecnicos-agropecuarios-siete-regiones-1094371.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>ERM 2026: ODPE Lambayeque y Cajamarca despliegan material electoral hacia zonas alejadas</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>El despliegue prioriza las zonas más alejadas y de difícil acceso de la jurisdicción.
 Como parte de este operativo, este viernes 2 de octubre se hizo el primer traslado hacia los centros poblados y algunos distritos, con material electoral y personal de la ODPE, del Jurado Nacional de Elecciones (JNE), de la Policía Nacional del Perú (PNP) y de las Fuerzas Armadas.
@@ -1496,166 +1671,9 @@
 Más en Andina: ?? ONPE inicia despliegue de material electoral en Lima Metropolitana y Callao por las Elecciones Regionales y Municipales 2026 https://t.co/OUu0kJCkd2 pic.twitter.com/UdJ7X3FW4w (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 3, 2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-erm-2026-odpe-lambayeque-y-cajamarca-despliegan-material-electoral-hacia-zonas-alejadas-1094390.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>INIA lanza concurso de becas para profesionales y técnicos agropecuarios en siete regiones</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>El objetivo de estas becas es fortalecer la capacidad técnica de profesionales y técnicos agropecuarios “para brindar servicios de calidad a las familias agricultoras del país”, detalló el INIA, en una nota de prensa.
-La convocatoria está dirigida a extensionistas agrarios, profesionales y técnicos agropecuarios “que cuenten con experiencia en la prestación de servicios de extensión agropecuaria dirigidos a productores de la agricultura familiar”, precisó la institución.
-En total, se otorgarán 510 becas para participar en los 12 cursos de formación y acreditación de PSEA, distribuidos en los departamentos de Lambayeque, Cajamarca, San Martín, Junín, Puno, Cusco y la provincia de Tayacaja (Huancavelica).
-[Lea también: Investigador del IIAP estudia cómo las aves contribuyen a la regeneración de los bosques ] Mejora de la productividad La propuesta de formación fortalecerá las capacidades de dichos profesionales para brindar servicios de extensión agropecuaria, con enfoque de género e intercultural, intergeneracional y de resiliencia al cambio climático.
-Para ello, se actualizarán sus conocimientos en aprendizaje adulto, enfoques y metodologías de extensión agropecuaria, financiamiento y comercialización, así como en innovaciones agrarias frugales pertinentes para la agricultura familiar, en los cultivos y crianzas priorizados.
-El proyecto PRED-INIA busca contribuir en la mejora de la productividad en el sector agrario del Perú, considerando la sostenibilidad ambiental y la resiliencia climática, propiciando un mayor acceso de las familias agricultoras a los servicios de innovación, transferencia tecnológica y extensión agropecuaria.
-Las bases del concurso se encuentran publicadas en la página web del INIA y las personas interesadas las pueden revisarlas visitando este enlace: clic aquí.
-[Lea también: Productores agrarios cuentan con Seguro Agrícola Catastrófico: cubre S/1,000 por hectárea ] Más en Andina: ?? Más de 13,000 lotes serán atendidos en octubre durante la “Maratón de la Titulación”, que llegará a 24 regiones.
-Cofopri realizará empadronamientos y atenderá casos pendientes para avanzar hacia la titulación.
-?? https://t.co/nGPPA4aFWe pic.twitter.com/fgn0V1jlXr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-inia-lanza-concurso-becas-para-profesionales-y-tecnicos-agropecuarios-siete-regiones-1094371.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Otass capacitó a profesionales de siete EPS para identificar brechas y mejorar servicios</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>La jornada estuvo orientada a identificar brechas y definir acciones para mejorar la prestación de los servicios de agua potable y saneamiento en beneficio de la población.
-Profesionales de EPS Marañón, Epsel, Sedalib, EPS Chavín, UE 002 Tumbes, Seda Chimbote y EPS Grau, analizaron información de sus propias empresas relacionada con aspectos financieros, continuidad y presión del servicio, pérdidas de agua e información comercial.
-“A partir de este análisis, cada prestadora elaboró un diagnóstico y una hoja de ruta con acciones para los próximos 90 y 180 días”, explicó el Otass en una nota de prensa.
-“Buscamos que las EPS puedan identificar sus brechas, tomar decisiones oportunas y prevenir problemas que puedan afectar los servicios.
-Ese conocimiento debe traducirse en empresas mejor preparadas para atender a más familias”, señaló el presidente ejecutivo del Otass.
-La asistencia técnica i ncluyó la revisión de programas de inversiones y fondos de reserva frente al Fenómeno El Niño (FEN), así como el uso de herramientas financieras como el costo promedio ponderado de capital (WACC), que permite determinar el valor presente de los flujos de caja futuros y evaluar proyectos de inversión.
-Estos conocimientos contribuyen a fortalecer la gestión financiera y a promover decisiones tarifarias técnicamente sustentadas que permitan financiar mejoras y sostener los servicios, considerando la capacidad de pago de la población.
-[Lea también: Lambayeque refuerza inspecciones de seguridad en escenarios que recibirán al papa León XIV ] Estrategia con resultados La estrategia ya fue aplicada en las macrorregiones Sur y Oriente, con la participación de más de 90 profesionales de 18 EPS.
-Las evaluaciones evidenciaron que el 100 % de los participantes mejoró sus conocimientos, elevando el promedio de sus calificaciones de 9.94 a 17.06 puntos sobre 20.
-Asimismo, profesionales de siete EPS alcanzaron la calificación máxima de 20 puntos.
-“De esta manera, el Otass combina capacitación, asistencia técnica y seguimiento de acuerdo con la situación de cada prestadora: en las EPS bajo el Régimen de Apoyo Transitorio (RAT), para contribuir a superar las condiciones que determinaron su ingreso al régimen y avanzar hacia una gestión sostenible; y en las demás prestadoras, para identificar brechas de manera anticipada y prevenir su deterioro, contribuyendo a servicios de agua potable y saneamiento más confiables para la población”, refirió la institución.
-[Lea también: Inician ejecución de cuatro proyectos eléctricos en beneficio de 1.6 millones de peruanos ] Más en Andina: ?? Más de 13,000 lotes serán atendidos en octubre durante la “Maratón de la Titulación”, que llegará a 24 regiones.
-Cofopri realizará empadronamientos y atenderá casos pendientes para avanzar hacia la titulación.
-?? https://t.co/nGPPA4aFWe pic.twitter.com/fgn0V1jlXr (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-otass-capacito-a-profesionales-siete-eps-para-identificar-brechas-y-mejorar-servicios-1094360.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Inician ejecución de cuatro proyectos eléctricos en beneficio de 1.6 millones de peruanos</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Los proyectos integran el Grupo 1, de los 4 que se formaron para licitar 17 proyectos de líneas de transmisión que provienen de los Planes de Transmisión 2023-2032 y 2025-2034; y que fueron encargados por el Ministerio de Energía y Minas (Minem) al inicio del año 2023 y 2025.
-Ministerio de Vivienda impulsa formalizar 13,000 lotes para cumplir meta de titulación El Grupo 1 representa una inversión superior a 339 millones de dólares, conforme a la oferta del adjudicatario, y es el resultado de un proceso de adjudicación muy competitivo en el que participaron y presentaron ofertas cuatro operadores de prestigio internacional.
-La ejecución de estos proyectos fortalecerá el Sistema Eléctrico Interconectado Nacional (SEIN), incrementará la capacidad de transmisión y mejorará la confiabilidad del suministro en estas cuatro regiones.
-Para la población, esta infraestructura contribuirá a una mayor continuidad del servicio eléctrico y permitirá atender la creciente demanda de los hogares, comercios, industrias y servicios.
-Así, facilitará el desarrollo de actividades económicas que requieren energía confiable para producir, crecer y generar oportunidades.
-El presidente ejecutivo de ProInversión, Luis Del Carpio, destacó que la suscripción de los contratos constituye un paso decisivo para hacer realidad estas inversiones y fortalecer las actividades productivas de las regiones beneficiarias.
-Asimismo, resaltó el compromiso de la Agencia con la promoción de infraestructura que responda a las necesidades de la población y contribuya al desarrollo descentralizado.
-“Invertir en transmisión eléctrica es invertir en competitividad, descentralización y desarrollo territorial.
-Una irrigación necesita energía para impulsar la agroindustria; un puerto, para operar y crecer; y un parque industrial, para atraer nuevas empresas.
-La energía confiable es la base que permite transformar el potencial de nuestras regiones en desarrollo”, agregó.
-Fortalecimiento regional En Piura, el Enlace 500 kV Miguel Grau–Pariñas y la subestación Pariñas 500/220 kV, con ampliaciones y subestaciones asociadas, mejorarán la confiabilidad del sistema y ampliarán la capacidad para incorporar energía renovable, principalmente eólica.
-Su área de influencia comprende Castilla y Pariñas.
-En Lambayeque, los Enlaces 220 kV Felam–Tierras Nuevas–Salitral, con ampliaciones y subestaciones asociadas, fortalecerán el suministro en el ámbito de Olmos, Motupe y Jayanca, brindando mayor respaldo a las actividades económicas y a los hogares.
-En Junín, la nueva subestación Palián 220/60 kV y sus enlaces asociados incrementarán la capacidad de suministro y reforzarán la continuidad del servicio ante contingencias.
-El proyecto comprende Huancayo, Orcotuna y Pucará.
-En Ayacucho, el Enlace 220 kV Muyurina–Mollepata, con ampliaciones y subestaciones asociadas, fortalecerá la confiabilidad de la transmisión eléctrica en la zona y mejorará las condiciones de operación ante contingencias.
-Los cuatro proyectos se desarrollarán mediante Asociaciones Público-Privadas (APP).
-ENGIE Transmisión Perú S.A., constituida por el adjudicatario ENGIE Energía Perú S.A.A., asumirá el diseño, financiamiento, construcción, operación y mantenimiento.
-Cada concesión comprende el periodo de construcción y 30 años de operación y mantenimiento.
-El acto contó con la participación de Luis Enrique Santillan, viceministro de Electricidad del Ministerio de Energía y Minas; José Marcelo Salazar, presidente de la Comisión de Economía, Banca, Finanzas e Inteligencia Financiera de la Cámara de Diputados; Dalia Miroslava Suárez, viceministra de Comunicaciones del Ministerio de Transportes y Comunicaciones; Carlos Alberto Lezameta, viceministro de Construcción y Saneamiento del Ministerio de Vivienda, Construcción y Saneamiento; y representantes de la concesionaria.
-ProInversión prevé adjudicar los siguientes Grupos 2 y 3 de transmisión eléctrica durante el cuarto trimestre de 2026, y el Grupo 4 durante el primer trimestre de 2027, para seguir fortaleciendo el suministro eléctrico y las oportunidades de desarrollo en el país.
-Más en Andina: ?? Perú busca movilizar US$5,800 millones al 2030 en financiamiento verde para proyectos ambientales.
-El Minam destaca avances en bionegocios y plantea ampliar inversiones para biodiversidad y acción climática.
-?? https://t.co/t0p87tZAdg pic.twitter.com/UTOOZGRk7e (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-inician-ejecucion-cuatro-proyectos-electricos-beneficio-16-millones-peruanos-1094342.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>46297</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Hallazgo en Huancavelica: descubren nueva especie de rana marsupial en Tayacaja</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>El hallazgo fue realizado por un equipo de investigadores y recientemente publicado en la revista científica internacional Zootaxa, donde se presentan las características que permiten diferenciar a esta nueva especie de otros anfibios del género Gastrotheca, informó el Servicio Nacional de Áreas Naturales Protegidas por el Estado (Sernanp).
-La investigación fue desarrollada por Víctor J.
-Vargas, de la Asociación Pro Fauna Silvestre Ayacucho, la Colección Científica Pro Fauna Silvestre Ayacucho y el Servicio Nacional Forestal y de Fauna Silvestre (Serfor); Kevin Rivera, afiliado a las mismas instituciones científicas, y Alessandro Catenazzi, de la Universidad Internacional de Florida y del Instituto Peruano de Herpetología.
-Lea también: Hallazgo en Arequipa: descubren nueva especie de lagartija que vive hasta los 4,800 metros Una rana de los bosques del Mantaro Gastrotheca amaru fue registrada en bosques húmedos de la cuenca baja del río Mantaro, a 2,590 metros sobre el nivel del mar.
-Para determinar que los ejemplares correspondían a una especie desconocida para la ciencia, los investigadores realizaron un análisis que combinó diferentes tipos de evidencia, entre ellos características morfológicas, información bioacústica y datos genéticos.
-Entre los rasgos que permiten distinguir a la nueva especie destaca su coloración dorado-amarilla, además de una combinación particular de características de la cabeza y el hocico que la diferencia de otras especies del mismo género.
-El descubrimiento amplía el conocimiento sobre la diversidad de anfibios de los bosques nublados de Huancavelica y pone en evidencia la presencia de especies que todavía no habían sido descritas científicamente en estos ecosistemas.
-Dos nuevos registros para Huancavelica Sernanp informó también que la investigación también permitió documentar por primera vez para Huancavelica la presencia de otras dos especies de anfibios: Hyloscirtus armatus y Rhinella leptoscelis.
-Estos registros amplían la distribución conocida de ambas especies y aportan nueva información sobre la composición de la fauna de anfibios de la región.
-De esta manera, el estudio no solo incorpora una nueva especie al conocimiento científico, sino que también incrementa la información disponible sobre la distribución de los anfibios en los Andes peruanos.
-Más en Andina: ??? Lambayeque reforzará las inspecciones de seguridad en los escenarios que recibirán al papa León XIV.
-Se evaluarán aforo, distribución de espacios, acondicionamiento y planes de contingencia.
-?? https://t.co/d7Np6YzLue pic.twitter.com/0ankkmI2CF (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-hallazgo-huancavelica-descubren-nueva-especie-rana-marsupial-tayacaja-1094321.aspx</t>
         </is>
       </c>
     </row>
@@ -1670,29 +1688,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda impulsa formalizar 13,000 lotes para cumplir meta de titulación</t>
+          <t>El Niño: Ejército del Perú acelera trabajos de descolmatación en río Piura</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A través del Organismo de Formalización de la Propiedad Informal (Cofopri), el sector desplegará sus brigadas en dos frentes de intervención: por un lado, llegará por primera vez a pueblos y sectores recientemente formalizados, cuyos terrenos ya cuentan con inscripción en Registros Públicos; y, por otro, retornará a zonas previamente visitadas para completar información, levantar observaciones y destrabar los casos que quedaron pendientes.
-Esta intervención forma parte de las acciones del Ministerio de Vivienda para acelerar los procesos de formalización de la propiedad y avanzar hacia la meta de alcanzar un millón de títulos entregados durante la actual gestión.
-Desde el inicio de la gestión del ministro Mauricio Arnillas, el Ministerio de Vivienda, Construcción y Saneamiento ha entregado más de 10,000 títulos de propiedad en diversas regiones del país.
-Más de 6,000 lotes iniciarán camino a titulación Las brigadas del Cofopri llegarán por primera vez a 34 pueblos para registrar más de 6,000 lotes como parte de un empadronamiento masivo y gratuito de los posesionarios, a quienes se solicitará información y documentación necesaria para avanzar hacia la titulación individual.
-En ese sentido, la región Piura concentrará una parte importante de este despliegue, con cinco pueblos que reúnen 1,350 lotes.
-También se intervendrá en Lambayeque, con 630 lotes; Cusco, con 497; Pasco, con 450, y Apurímac, con 405, entre otras regiones.
-Más de 7,000 lotes tendrán nueva oportunidad Las brigadas también retornarán a zonas que ya fueron visitadas anteriormente para ubicar a los posesionarios, completar información, levantar observaciones y continuar con el proceso de titulación individual.
-En este caso, Puno tendrá el mayor despliegue, con 1,890 lotes que serán nuevamente visitados.
-Le siguen Junín, con 601; Lima, con 561; Huancavelica, con 410, y Ayacucho, con 400 lotes, entre otras regiones.
-Las fechas y lugares de las visitas pueden consultarse en el siguiente enlace o mediante la línea gratuita 0800-28-028.
-Más en Andina: ?? Perú puede acceder a créditos con condiciones favorables debido a sus buenos datos macroeconómicos, destacó la Cooperación Alemana al Desarrollo.
-Los préstamos dependen del tipo de proyecto y pueden ser de largo plazo.
-?? https://t.co/TrNFz7YnN1 pic.twitter.com/G4P8nsiIyL (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 2, 2026</t>
+          <t>Desde el puente Independencia, en el asentamiento humano Juan de Mori del distrito de Catacaos, el titular del sector señaló que las labores de descolmatación y encauzamiento del afluente, así como el reforzamiento de diques, se encuentran dentro del cronograma previsto e incluso adelantado.
+"Estamos viniendo semanalmente, o cada diez días, para ver el progreso y nos complace constatar que estamos o dentro del cronograma de avance o, incluso, lo hemos superado.
+Y, eso nos deja tranquilos, porque vamos a llegar a tiempo ante el embate del fenómeno El Niño” , subrayó.
+Registro fotográfico Belaunde Llosa refirió que cada semana el satélite PerúSAT-1, operado por la Agencia Espacial del Perú (Conida), entrega a su despacho un registro fotográfico de los avances de las labores del Ejército en la zona y el avance está dentro del cronograma establecido.
+"Hace quince días, aquí había un bosque.
+Es evidente el avance.
+Vamos a llegar a recibir los embates del fenómeno El Niño de la manera más preparada posible" , enfatizó tras remarcar que el Gobierno priorizó la intervención de puntos críticos ante la cercanía del evento climático y el abandono de los gobiernos anteriores a desarrollar trabajos de prevención.
+22 puntos críticos "Todos los puntos críticos que representen peligro, primero, a la vida y, después, a la propiedad pública-privada se atenderán.
+Es materialmente imposible cubrir los dos mil puntos críticos recibidos de la ANA (Autoridad Nacional del Agua), porque en sesenta días no se puede atender lo que se ha dejado de hacer en nueve años" , sostuvo.
+Según lo dispuesto por el Poder Ejecutivo, al sector Defensa le corresponde intervenir 22 puntos críticos ubicados a lo largo del litoral peruano: en Tumbes, 3 puntos; en Piura, 7; en Lambayeque, 2; en La Libertad, 1; en Lima, 7; y en Ica, 2.
+Más en Andina: Programa Llamkasun Perú proyecta generar más de 59,000 empleos temporales hasta diciembre https://t.co/ZtQLMBwXBs pic.twitter.com/jaeLjluJR7 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 3, 2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-ministerio-vivienda-impulsa-formalizar-13000-lotes-para-cumplir-meta-titulacion-1094304.aspx</t>
+          <t>https://andina.pe/agencia/noticia-el-nino-ejercito-del-peru-acelera-trabajos-descolmatacion-rio-piura-1094393.aspx</t>
         </is>
       </c>
     </row>
